--- a/data/trans_camb/IP1011-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Clase-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,0</t>
+          <t>-1,85; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,68</t>
+          <t>-1,25; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,87; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,33</t>
+          <t>-0,52; 0,33</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,61</t>
+          <t>-0,83; 8,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,0</t>
+          <t>-4,66; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 0,0</t>
+          <t>-4,15; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,65</t>
+          <t>-1,24; 2,49</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-2,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,54</t>
+          <t>-0,19; 0,57</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,0</t>
+          <t>-0,44; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,2</t>
+          <t>-0,48; 0,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,26</t>
+          <t>-0,22; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">

--- a/data/trans_camb/IP1011-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Clase-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,93</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,0</t>
+          <t>-1,94; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,68</t>
+          <t>-1,05; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,0</t>
+          <t>-1,04; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,33</t>
+          <t>-0,61; 0,33</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,7</t>
+          <t>-0,82; 7,47</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 0,0</t>
+          <t>-4,16; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 0,0</t>
+          <t>-4,18; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,49</t>
+          <t>-1,24; 2,69</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,57</t>
+          <t>-0,19; 0,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 0,0</t>
+          <t>-0,48; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,19</t>
+          <t>-0,47; 0,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,2</t>
+          <t>-0,45; 0,2</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,26</t>
+          <t>-0,22; 0,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,06</t>
+          <t>-0,32; 0,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1011-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1011-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,7 +593,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,01</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,05; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,0</t>
+          <t>-0,82; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,33</t>
+          <t>-0,53; 0,33</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,44%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,83</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>1,81</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>-0,81</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,83</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,47</t>
+          <t>-4,22; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-5,0; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,0</t>
+          <t>-0,82; 7,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,0</t>
+          <t>-4,76; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,69</t>
+          <t>-1,25; 2,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
     </row>
@@ -1449,17 +1449,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>224,06%</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 0,54</t>
+          <t>-0,48; 0,19</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,0</t>
+          <t>-0,45; 0,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,19</t>
+          <t>-0,17; 0,54</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,2</t>
+          <t>-0,63; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,24</t>
+          <t>-0,2; 0,26</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,06</t>
+          <t>-0,33; 0,06</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-50,53%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-47,2%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>121,15%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-50,53%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-47,2%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
